--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>68053900</v>
       </c>
       <c r="B2" t="n">
-        <v>88994</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449439.4637019665</v>
+        <v>449439</v>
       </c>
       <c r="R2" t="n">
-        <v>6218010.856154202</v>
+        <v>6218011</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2017-10-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +772,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68053819</v>
+        <v>127724001</v>
       </c>
       <c r="B3" t="n">
-        <v>87558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3483</v>
+        <v>1265</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rutbläcksvamp</t>
+          <t>Stor tratticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coprinopsis picacea</t>
+          <t>Picipes badius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
+          <t>(Pers.) Zmitr. &amp; Kovalenko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Balsberget, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449439.4637019665</v>
+        <v>449457</v>
       </c>
       <c r="R3" t="n">
-        <v>6218010.856154202</v>
+        <v>6218205</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,21 +854,230 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Mikael Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mikael Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111970467</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92532</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stenticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polyporus tuberaster</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Jacq. ex Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Balsberget, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>449611</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6218138</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fjälkestad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>bokskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>bokgren på marken</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tony Svensson, Nils Otto Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>68053819</v>
+      </c>
+      <c r="B5" t="n">
+        <v>88540</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3483</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rutbläcksvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Coprinopsis picacea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Balsberget, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>449439</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6218011</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fjälkestad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-10-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-10-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68053900</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127724001</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111970467</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,8 +1098,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68053819</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,112 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/68053819</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136257279</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75417</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6427</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Glansfläck</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Diarthonis spadicea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Leight.) Frisch &amp; al.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gamlegård NO, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>449479</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6218244</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fjälkestad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136257279</t>
         </is>
       </c>
     </row>
@@ -1110,6 +1216,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1109,7 +1109,7 @@
         <v>136257279</v>
       </c>
       <c r="B6" t="n">
-        <v>75417</v>
+        <v>75418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1109,7 +1109,7 @@
         <v>136257279</v>
       </c>
       <c r="B6" t="n">
-        <v>75418</v>
+        <v>75422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1109,7 +1109,7 @@
         <v>136257279</v>
       </c>
       <c r="B6" t="n">
-        <v>75422</v>
+        <v>75423</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1109,7 +1109,7 @@
         <v>136257279</v>
       </c>
       <c r="B6" t="n">
-        <v>75423</v>
+        <v>75427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1109,7 +1109,7 @@
         <v>136257279</v>
       </c>
       <c r="B6" t="n">
-        <v>75427</v>
+        <v>75433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1109,7 +1109,7 @@
         <v>136257279</v>
       </c>
       <c r="B6" t="n">
-        <v>75433</v>
+        <v>75446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1109,7 +1109,7 @@
         <v>136257279</v>
       </c>
       <c r="B6" t="n">
-        <v>75446</v>
+        <v>75447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
